--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-15).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-15).xlsx
@@ -915,66 +915,66 @@
   </si>
   <si>
     <t>215
-139</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>R$ 758.720,61</t>
-  </si>
-  <si>
-    <t>R$ 5.058,14
-R$ 5.240,59</t>
-  </si>
-  <si>
-    <t>9.3%
-13.2%</t>
-  </si>
-  <si>
-    <t>56.5</t>
-  </si>
-  <si>
-    <t>7.2%</t>
-  </si>
-  <si>
-    <t>48.1%</t>
-  </si>
-  <si>
-    <t>4.9%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>26.6</t>
-  </si>
-  <si>
-    <t>70.2%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>6.9</t>
-  </si>
-  <si>
-    <t>12.2</t>
-  </si>
-  <si>
-    <t>18.6</t>
-  </si>
-  <si>
-    <t>74.1%</t>
-  </si>
-  <si>
-    <t>-R$ 16.861,46</t>
+171</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R$ 907.654,06</t>
+  </si>
+  <si>
+    <t>R$ 4.932,90
+R$ 5.074,50</t>
+  </si>
+  <si>
+    <t>11.4%
+14.6%</t>
+  </si>
+  <si>
+    <t>55.0</t>
+  </si>
+  <si>
+    <t>8.1%</t>
+  </si>
+  <si>
+    <t>42.1%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>27.2</t>
+  </si>
+  <si>
+    <t>67.8%</t>
+  </si>
+  <si>
+    <t>10.5%</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>19.2</t>
+  </si>
+  <si>
+    <t>72.2%</t>
+  </si>
+  <si>
+    <t>-R$ 20.504,06</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2216,10 +2216,10 @@
         <v>-0.13924050632911389</v>
       </c>
       <c r="T7" s="6">
-        <v>0.34621314682434617</v>
+        <v>0.34887242961786247</v>
       </c>
       <c r="U7" s="6">
-        <v>0.028346233047980465</v>
+        <v>0.031005515841496776</v>
       </c>
       <c r="V7" s="6">
         <v>0.041042199864678018</v>
@@ -2950,7 +2950,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>44</v>
@@ -2986,25 +2986,61 @@
       <c t="s" r="N13" s="4">
         <v>52</v>
       </c>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="6"/>
+      <c r="O13" s="5">
+        <v>6247.6599999999999</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6247.6599999999999</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>0.09457326313760861</v>
+      </c>
+      <c r="R13" s="7">
+        <v>77</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0.18461538461538463</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0.35381562056834076</v>
+      </c>
+      <c r="U13" s="6">
+        <v>0.0049458037089086153</v>
+      </c>
+      <c r="V13" s="6">
+        <v>0.04345554975782933</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.0094396141915533173</v>
+      </c>
+      <c r="X13" s="8">
+        <v>29.256665999999999</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z13" s="6">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AA13" s="8">
+        <v>7.1429162500000007</v>
+      </c>
+      <c r="AB13" s="8">
+        <v>6.5720000000000001</v>
+      </c>
+      <c r="AC13" s="8">
+        <v>13.906666</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>20.860333999999998</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>0.52000000000000002</v>
+      </c>
       <c r="AF13" s="9"/>
-      <c r="AG13" s="5"/>
+      <c r="AG13" s="5">
+        <v>-307.39999999999998</v>
+      </c>
       <c r="AH13" s="10">
         <v>5</v>
       </c>
@@ -4014,10 +4050,10 @@
         <v>0.93939393939393945</v>
       </c>
       <c r="T21" s="6">
-        <v>0.280521176378487</v>
+        <v>0.27370752329010206</v>
       </c>
       <c r="U21" s="6">
-        <v>-0.033078851456555591</v>
+        <v>-0.039892504544940546</v>
       </c>
       <c r="V21" s="6">
         <v>0.019164165862059969</v>
@@ -4712,7 +4748,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4748,25 +4784,61 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="O27" s="5">
+        <v>2674.0500000000002</v>
+      </c>
+      <c r="P27" s="5">
+        <v>2674.0500000000002</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.56517815329378707</v>
+      </c>
+      <c r="R27" s="7">
+        <v>38</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.37704918032786883</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.26919571436584955</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.14072556608889139</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.091989678577438713</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.076339260672014353</v>
+      </c>
+      <c r="X27" s="8">
+        <v>25.63095238095238</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>3.7395843750000002</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>8.7641650000000002</v>
+      </c>
+      <c r="AC27" s="8">
+        <v>12.931626</v>
+      </c>
+      <c r="AD27" s="8">
+        <v>20.3127</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.8571428571428571</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>0</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4807,7 +4879,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4843,25 +4915,61 @@
       <c t="s" r="N28" s="4">
         <v>52</v>
       </c>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="8"/>
-      <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="6"/>
+      <c r="O28" s="5">
+        <v>5495.1999999999998</v>
+      </c>
+      <c r="P28" s="5">
+        <v>5495.1999999999998</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>1.337706535981078</v>
+      </c>
+      <c r="R28" s="7">
+        <v>53</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0.96296296296296302</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0.00024475906245450575</v>
+      </c>
+      <c r="U28" s="6">
+        <v>-0.32041326976270201</v>
+      </c>
+      <c r="V28" s="6">
+        <v>0.077358967826466743</v>
+      </c>
+      <c r="W28" s="6">
+        <v>0.068897037414470813</v>
+      </c>
+      <c r="X28" s="8">
+        <v>21.176785714285717</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="8">
+        <v>2.1305555555555555</v>
+      </c>
+      <c r="AB28" s="8">
+        <v>5.2922607142857148</v>
+      </c>
+      <c r="AC28" s="8">
+        <v>7.6503059999999996</v>
+      </c>
+      <c r="AD28" s="8">
+        <v>14.659525</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>0.8928571428571429</v>
+      </c>
       <c r="AF28" s="9"/>
-      <c r="AG28" s="5"/>
+      <c r="AG28" s="5">
+        <v>-1237.8800000000001</v>
+      </c>
       <c r="AH28" s="10">
         <v>2</v>
       </c>
@@ -6212,7 +6320,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6248,25 +6356,61 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="O39" s="5">
+        <v>7382.3800000000001</v>
+      </c>
+      <c r="P39" s="5">
+        <v>7382.3800000000001</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>0.74396541541659755</v>
+      </c>
+      <c r="R39" s="7">
+        <v>81</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0.47272727272727266</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.26325804144462894</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.034048518228538764</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.069983121974214288</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.035151536496360256</v>
+      </c>
+      <c r="X39" s="8">
+        <v>19.994444444444444</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>2.3506493506493507</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>5.850407317073171</v>
+      </c>
+      <c r="AC39" s="8">
+        <v>8.2016399999999994</v>
+      </c>
+      <c r="AD39" s="8">
+        <v>13.760494444444443</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.90740740740740744</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6664,7 +6808,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6700,25 +6844,61 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="O43" s="5">
+        <v>7644.8500000000004</v>
+      </c>
+      <c r="P43" s="5">
+        <v>7644.8500000000004</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>0.48878182345758603</v>
+      </c>
+      <c r="R43" s="7">
+        <v>68</v>
+      </c>
+      <c r="S43" s="6">
+        <v>0.2592592592592593</v>
+      </c>
+      <c r="T43" s="6">
+        <v>-0.0001815078124489035</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.33531300156314381</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.014987344421407874</v>
+      </c>
+      <c r="W43" s="6">
+        <v>-0.0032837792762447919</v>
+      </c>
+      <c r="X43" s="8">
+        <v>41.947386274509803</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.50980392156862742</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>8.6801927536231887</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>13.099019607843136</v>
+      </c>
+      <c r="AC43" s="8">
+        <v>22.025621000000001</v>
+      </c>
+      <c r="AD43" s="8">
+        <v>29.084641176470591</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.13725490196078433</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -6759,7 +6939,7 @@
         <v>19581</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>44</v>
@@ -6795,25 +6975,61 @@
       <c t="s" r="N44" s="4">
         <v>52</v>
       </c>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="8"/>
-      <c r="Y44" s="6"/>
-      <c r="Z44" s="6"/>
-      <c r="AA44" s="8"/>
-      <c r="AB44" s="8"/>
-      <c r="AC44" s="8"/>
-      <c r="AD44" s="8"/>
-      <c r="AE44" s="6"/>
+      <c r="O44" s="5">
+        <v>6925.0600000000004</v>
+      </c>
+      <c r="P44" s="5">
+        <v>6925.0600000000004</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>0.62744614198727677</v>
+      </c>
+      <c r="R44" s="7">
+        <v>66</v>
+      </c>
+      <c r="S44" s="6">
+        <v>0.4042553191489362</v>
+      </c>
+      <c r="T44" s="6">
+        <v>0.35616790323838349</v>
+      </c>
+      <c r="U44" s="6">
+        <v>0.012332615168677239</v>
+      </c>
+      <c r="V44" s="6">
+        <v>0.023469760550811111</v>
+      </c>
+      <c r="W44" s="6">
+        <v>0.0030280604066968372</v>
+      </c>
+      <c r="X44" s="8">
+        <v>22.567334000000002</v>
+      </c>
+      <c r="Y44" s="6">
+        <v>0.47999999999999998</v>
+      </c>
+      <c r="Z44" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="8">
+        <v>3.388725</v>
+      </c>
+      <c r="AB44" s="8">
+        <v>7.0625</v>
+      </c>
+      <c r="AC44" s="8">
+        <v>10.524918</v>
+      </c>
+      <c r="AD44" s="8">
+        <v>17.256</v>
+      </c>
+      <c r="AE44" s="6">
+        <v>0.83999999999999997</v>
+      </c>
       <c r="AF44" s="9"/>
-      <c r="AG44" s="5"/>
+      <c r="AG44" s="5">
+        <v>-59.899999999999999</v>
+      </c>
       <c r="AH44" s="10">
         <v>3</v>
       </c>
@@ -6985,7 +7201,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -7019,25 +7235,61 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="O46" s="5">
+        <v>5749.25</v>
+      </c>
+      <c r="P46" s="5">
+        <v>5749.25</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>0.28097009937168571</v>
+      </c>
+      <c r="R46" s="7">
+        <v>51</v>
+      </c>
+      <c r="S46" s="6">
+        <v>0</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0.46433393920946209</v>
+      </c>
+      <c r="U46" s="6">
+        <v>0.023530356133408706</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.044870983171718046</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.0012359003348262818</v>
+      </c>
+      <c r="X46" s="8">
+        <v>22.147915625</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>2.5427679245283015</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>6.9827586206896548</v>
+      </c>
+      <c r="AC46" s="8">
+        <v>9.4268750000000008</v>
+      </c>
+      <c r="AD46" s="8">
+        <v>15.201040624999999</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.84375</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>82.400000000000006</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -7467,7 +7719,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7503,25 +7755,61 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="O50" s="5">
+        <v>5863.8800000000001</v>
+      </c>
+      <c r="P50" s="5">
+        <v>5863.8800000000001</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>0.84764785581497959</v>
+      </c>
+      <c r="R50" s="7">
+        <v>69</v>
+      </c>
+      <c r="S50" s="6">
+        <v>0.68292682926829262</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.18216054898804204</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.11380219240502876</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.087297062695689542</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.046643092969160353</v>
+      </c>
+      <c r="X50" s="8">
+        <v>21.361806250000001</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>3.1571032786885249</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>4.2981891304347828</v>
+      </c>
+      <c r="AC50" s="8">
+        <v>7.5549249999999999</v>
+      </c>
+      <c r="AD50" s="8">
+        <v>15.077083333333334</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.9375</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>153.19999999999999</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7788,7 +8076,7 @@
         <v>19607</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>44</v>
@@ -7822,25 +8110,59 @@
       <c t="s" r="N53" s="4">
         <v>52</v>
       </c>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="7"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
-      <c r="X53" s="8"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
-      <c r="AA53" s="8"/>
-      <c r="AB53" s="8"/>
+      <c r="O53" s="5">
+        <v>5386.8400000000001</v>
+      </c>
+      <c r="P53" s="5">
+        <v>5386.8400000000001</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>0.84891762856485808</v>
+      </c>
+      <c r="R53" s="7">
+        <v>53</v>
+      </c>
+      <c r="S53" s="6">
+        <v>0.39473684210526305</v>
+      </c>
+      <c r="T53" s="6">
+        <v>0.31547135240697699</v>
+      </c>
+      <c r="U53" s="6">
+        <v>-0.022801178427426839</v>
+      </c>
+      <c r="V53" s="6">
+        <v>0.031363285339828177</v>
+      </c>
+      <c r="W53" s="6">
+        <v>0.0062353810397190188</v>
+      </c>
+      <c r="X53" s="8">
+        <v>22.206668000000001</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>0.76000000000000001</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="8">
+        <v>4.3872549019607847</v>
+      </c>
+      <c r="AB53" s="8">
+        <v>2.901332</v>
+      </c>
       <c r="AC53" s="8"/>
-      <c r="AD53" s="8"/>
-      <c r="AE53" s="6"/>
+      <c r="AD53" s="8">
+        <v>13.347999999999999</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0.95999999999999996</v>
+      </c>
       <c r="AF53" s="9"/>
-      <c r="AG53" s="5"/>
+      <c r="AG53" s="5">
+        <v>0</v>
+      </c>
       <c r="AH53" s="10">
         <v>3</v>
       </c>
@@ -7881,7 +8203,7 @@
         <v>19609</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>44</v>
@@ -7917,25 +8239,61 @@
       <c t="s" r="N54" s="4">
         <v>52</v>
       </c>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="7"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="8"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-      <c r="AA54" s="8"/>
-      <c r="AB54" s="8"/>
-      <c r="AC54" s="8"/>
-      <c r="AD54" s="8"/>
-      <c r="AE54" s="6"/>
+      <c r="O54" s="5">
+        <v>4513.0500000000002</v>
+      </c>
+      <c r="P54" s="5">
+        <v>4513.0500000000002</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>0.56755921265148324</v>
+      </c>
+      <c r="R54" s="7">
+        <v>47</v>
+      </c>
+      <c r="S54" s="6">
+        <v>0.17500000000000004</v>
+      </c>
+      <c r="T54" s="6">
+        <v>0.33374055239804562</v>
+      </c>
+      <c r="U54" s="6">
+        <v>-0.02200999324182094</v>
+      </c>
+      <c r="V54" s="6">
+        <v>0.012693854488649582</v>
+      </c>
+      <c r="W54" s="6">
+        <v>-0.028533253564662475</v>
+      </c>
+      <c r="X54" s="8">
+        <v>51.899999999999999</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0.29729729729729731</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AA54" s="8">
+        <v>6.268402083333334</v>
+      </c>
+      <c r="AB54" s="8">
+        <v>27.006756756756758</v>
+      </c>
+      <c r="AC54" s="8">
+        <v>33.466842999999997</v>
+      </c>
+      <c r="AD54" s="8">
+        <v>40.222521621621624</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>0.16216216216216217</v>
+      </c>
       <c r="AF54" s="9"/>
-      <c r="AG54" s="5"/>
+      <c r="AG54" s="5">
+        <v>0</v>
+      </c>
       <c r="AH54" s="10">
         <v>2</v>
       </c>
@@ -7976,7 +8334,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8012,25 +8370,61 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="O55" s="5">
+        <v>4514.6999999999998</v>
+      </c>
+      <c r="P55" s="5">
+        <v>4514.6999999999998</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>0.27787307032590047</v>
+      </c>
+      <c r="R55" s="7">
+        <v>55</v>
+      </c>
+      <c r="S55" s="6">
+        <v>0.14583333333333326</v>
+      </c>
+      <c r="T55" s="6">
+        <v>1.9934879393979666E-05</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.30262918909340597</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.11067811814738521</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.056014463862493633</v>
+      </c>
+      <c r="X55" s="8">
+        <v>24.089836585365855</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.17777777777777778</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>2.3593561403508776</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>8.5142268292682921</v>
+      </c>
+      <c r="AC55" s="8">
+        <v>10.895432</v>
+      </c>
+      <c r="AD55" s="8">
+        <v>17.708536585365852</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0.78048780487804881</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8688,7 +9082,7 @@
         <v>19624</v>
       </c>
       <c r="B61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C61" s="4">
         <v>44</v>
@@ -8722,25 +9116,61 @@
       <c t="s" r="N61" s="4">
         <v>52</v>
       </c>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="7"/>
-      <c r="S61" s="6"/>
-      <c r="T61" s="6"/>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
-      <c r="W61" s="6"/>
-      <c r="X61" s="8"/>
-      <c r="Y61" s="6"/>
-      <c r="Z61" s="6"/>
-      <c r="AA61" s="8"/>
-      <c r="AB61" s="8"/>
-      <c r="AC61" s="8"/>
-      <c r="AD61" s="8"/>
-      <c r="AE61" s="6"/>
+      <c r="O61" s="5">
+        <v>3225.0999999999999</v>
+      </c>
+      <c r="P61" s="5">
+        <v>3225.0999999999999</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>0.24356547120994199</v>
+      </c>
+      <c r="R61" s="7">
+        <v>39</v>
+      </c>
+      <c r="S61" s="6">
+        <v>0.14705882352941169</v>
+      </c>
+      <c r="T61" s="6">
+        <v>0.25164804192118073</v>
+      </c>
+      <c r="U61" s="6">
+        <v>-0.067073858174940312</v>
+      </c>
+      <c r="V61" s="6">
+        <v>0.045402778208427648</v>
+      </c>
+      <c r="W61" s="6">
+        <v>-0.010598586090353787</v>
+      </c>
+      <c r="X61" s="8">
+        <v>19.224446666666665</v>
+      </c>
+      <c r="Y61" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="8">
+        <v>1.7035078947368421</v>
+      </c>
+      <c r="AB61" s="8">
+        <v>4.5607142857142859</v>
+      </c>
+      <c r="AC61" s="8">
+        <v>5.7909220000000001</v>
+      </c>
+      <c r="AD61" s="8">
+        <v>12.343333333333334</v>
+      </c>
+      <c r="AE61" s="6">
+        <v>0.93333333333333335</v>
+      </c>
       <c r="AF61" s="9"/>
-      <c r="AG61" s="5"/>
+      <c r="AG61" s="5">
+        <v>-78.400000000000006</v>
+      </c>
       <c r="AH61" s="10">
         <v>3</v>
       </c>
@@ -9910,7 +10340,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9944,25 +10374,61 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="O71" s="5">
+        <v>5548.1599999999999</v>
+      </c>
+      <c r="P71" s="5">
+        <v>5548.1599999999999</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.32009783860437224</v>
+      </c>
+      <c r="R71" s="7">
+        <v>70</v>
+      </c>
+      <c r="S71" s="6">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="T71" s="6">
+        <v>-0.46712457823855119</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.79730070870342606</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.027505965941861804</v>
+      </c>
+      <c r="W71" s="6">
+        <v>-0.0067197953916253318</v>
+      </c>
+      <c r="X71" s="8">
+        <v>21.095833333333335</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>4.3948529411764712</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>4.2058349999999995</v>
+      </c>
+      <c r="AC71" s="8">
+        <v>7.3611659999999999</v>
+      </c>
+      <c r="AD71" s="8">
+        <v>14.254166666666668</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>0</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10352,7 +10818,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10388,25 +10854,61 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="O75" s="5">
+        <v>5034.3599999999997</v>
+      </c>
+      <c r="P75" s="5">
+        <v>5034.3599999999997</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>0.70843330154711759</v>
+      </c>
+      <c r="R75" s="7">
+        <v>47</v>
+      </c>
+      <c r="S75" s="6">
+        <v>0.17500000000000004</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.28322765952375278</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.040631480466236033</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.016733705972556592</v>
+      </c>
+      <c r="X75" s="8">
+        <v>28.748529411764707</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>5.6400702127659574</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>9.7730382352941181</v>
+      </c>
+      <c r="AC75" s="8">
+        <v>15.584803000000001</v>
+      </c>
+      <c r="AD75" s="8">
+        <v>22.514705882352942</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.61764705882352944</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-297.69999999999999</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10576,7 +11078,7 @@
         <v>19665</v>
       </c>
       <c r="B77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C77" s="4">
         <v>44</v>
@@ -10612,25 +11114,61 @@
       <c t="s" r="N77" s="4">
         <v>52</v>
       </c>
-      <c r="O77" s="5"/>
-      <c r="P77" s="5"/>
-      <c r="Q77" s="6"/>
-      <c r="R77" s="7"/>
-      <c r="S77" s="6"/>
-      <c r="T77" s="6"/>
-      <c r="U77" s="6"/>
-      <c r="V77" s="6"/>
-      <c r="W77" s="6"/>
-      <c r="X77" s="8"/>
-      <c r="Y77" s="6"/>
-      <c r="Z77" s="6"/>
-      <c r="AA77" s="8"/>
-      <c r="AB77" s="8"/>
-      <c r="AC77" s="8"/>
-      <c r="AD77" s="8"/>
-      <c r="AE77" s="6"/>
+      <c r="O77" s="5">
+        <v>4900.7600000000002</v>
+      </c>
+      <c r="P77" s="5">
+        <v>4900.7600000000002</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>0.12967850647389834</v>
+      </c>
+      <c r="R77" s="7">
+        <v>47</v>
+      </c>
+      <c r="S77" s="6">
+        <v>0</v>
+      </c>
+      <c r="T77" s="6">
+        <v>0.31566267272831156</v>
+      </c>
+      <c r="U77" s="6">
+        <v>-0.011417208759457717</v>
+      </c>
+      <c r="V77" s="6">
+        <v>0.016927170479680703</v>
+      </c>
+      <c r="W77" s="6">
+        <v>-0.010778736359258563</v>
+      </c>
+      <c r="X77" s="8">
+        <v>21.339167499999999</v>
+      </c>
+      <c r="Y77" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="8">
+        <v>2.7290787234042551</v>
+      </c>
+      <c r="AB77" s="8">
+        <v>3.5833333333333335</v>
+      </c>
+      <c r="AC77" s="8">
+        <v>6.543749</v>
+      </c>
+      <c r="AD77" s="8">
+        <v>13.176667499999999</v>
+      </c>
+      <c r="AE77" s="6">
+        <v>0.94999999999999996</v>
+      </c>
       <c r="AF77" s="9"/>
-      <c r="AG77" s="5"/>
+      <c r="AG77" s="5">
+        <v>-58.799999999999997</v>
+      </c>
       <c r="AH77" s="10"/>
       <c r="AI77" s="11">
         <v>4</v>
@@ -11689,10 +12227,10 @@
         <v>-0.34693877551020413</v>
       </c>
       <c r="T86" s="6">
-        <v>0.38288043528155286</v>
+        <v>0.39030323431575664</v>
       </c>
       <c r="U86" s="6">
-        <v>0.029073404798991363</v>
+        <v>0.036496203833195115</v>
       </c>
       <c r="V86" s="6">
         <v>0.049262340984830635</v>
@@ -13649,7 +14187,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -13685,25 +14223,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>3191.8800000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>3191.8800000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>0.095631041300527242</v>
+      </c>
+      <c r="R102" s="7">
+        <v>32</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.11111111111111116</v>
+      </c>
+      <c r="T102" s="6">
+        <v>3.9537827236612908E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.31967486246350113</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.014058329260498515</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.011462680301264457</v>
+      </c>
+      <c r="X102" s="8">
+        <v>51.889680952380949</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>7.0739593750000003</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>23.126315789473683</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>33.951585714285713</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.14285714285714285</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -14266,7 +14838,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>44</v>
@@ -14302,25 +14874,61 @@
       <c t="s" r="N107" s="4">
         <v>52</v>
       </c>
-      <c r="O107" s="5"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="7"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-      <c r="X107" s="8"/>
-      <c r="Y107" s="6"/>
-      <c r="Z107" s="6"/>
-      <c r="AA107" s="8"/>
-      <c r="AB107" s="8"/>
-      <c r="AC107" s="8"/>
-      <c r="AD107" s="8"/>
-      <c r="AE107" s="6"/>
+      <c r="O107" s="5">
+        <v>2802.1500000000001</v>
+      </c>
+      <c r="P107" s="5">
+        <v>2802.1500000000001</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>0.34191018015688313</v>
+      </c>
+      <c r="R107" s="7">
+        <v>30</v>
+      </c>
+      <c r="S107" s="6">
+        <v>0.034482758620689724</v>
+      </c>
+      <c r="T107" s="6">
+        <v>0.0061295433863283542</v>
+      </c>
+      <c r="U107" s="6">
+        <v>-0.34845889763217525</v>
+      </c>
+      <c r="V107" s="6">
+        <v>0.072950591510090465</v>
+      </c>
+      <c r="W107" s="6">
+        <v>0.030715165141052405</v>
+      </c>
+      <c r="X107" s="8">
+        <v>24.047368421052632</v>
+      </c>
+      <c r="Y107" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="8">
+        <v>5.1896551724137927</v>
+      </c>
+      <c r="AB107" s="8">
+        <v>5.8359631578947369</v>
+      </c>
+      <c r="AC107" s="8">
+        <v>11.512278999999999</v>
+      </c>
+      <c r="AD107" s="8">
+        <v>18.464036842105266</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>0.73684210526315785</v>
+      </c>
       <c r="AF107" s="9"/>
-      <c r="AG107" s="5"/>
+      <c r="AG107" s="5">
+        <v>-69.799999999999997</v>
+      </c>
       <c r="AH107" s="10">
         <v>2</v>
       </c>
@@ -15029,7 +15637,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>44</v>
@@ -15065,25 +15673,61 @@
       <c t="s" r="N114" s="4">
         <v>52</v>
       </c>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
-      <c r="V114" s="6"/>
-      <c r="W114" s="6"/>
-      <c r="X114" s="8"/>
-      <c r="Y114" s="6"/>
-      <c r="Z114" s="6"/>
-      <c r="AA114" s="8"/>
-      <c r="AB114" s="8"/>
-      <c r="AC114" s="8"/>
-      <c r="AD114" s="8"/>
-      <c r="AE114" s="6"/>
+      <c r="O114" s="5">
+        <v>6052.1199999999999</v>
+      </c>
+      <c r="P114" s="5">
+        <v>6052.1199999999999</v>
+      </c>
+      <c r="Q114" s="6">
+        <v>0.31272178311455079</v>
+      </c>
+      <c r="R114" s="7">
+        <v>46</v>
+      </c>
+      <c r="S114" s="6">
+        <v>-0.061224489795918324</v>
+      </c>
+      <c r="T114" s="6">
+        <v>-0.1663214047309042</v>
+      </c>
+      <c r="U114" s="6">
+        <v>-0.40834899175825995</v>
+      </c>
+      <c r="V114" s="6">
+        <v>0.016964633880359278</v>
+      </c>
+      <c r="W114" s="6">
+        <v>0.0079380448503995303</v>
+      </c>
+      <c r="X114" s="8">
+        <v>26.520731707317072</v>
+      </c>
+      <c r="Y114" s="6">
+        <v>0.51219512195121952</v>
+      </c>
+      <c r="Z114" s="6">
+        <v>0.097560975609756101</v>
+      </c>
+      <c r="AA114" s="8">
+        <v>4.1572916666666666</v>
+      </c>
+      <c r="AB114" s="8">
+        <v>6.7679487179487179</v>
+      </c>
+      <c r="AC114" s="8">
+        <v>10.301280999999999</v>
+      </c>
+      <c r="AD114" s="8">
+        <v>17.826017073170732</v>
+      </c>
+      <c r="AE114" s="6">
+        <v>0.75609756097560976</v>
+      </c>
       <c r="AF114" s="9"/>
-      <c r="AG114" s="5"/>
+      <c r="AG114" s="5">
+        <v>-126.40000000000001</v>
+      </c>
       <c r="AH114" s="10">
         <v>2</v>
       </c>
@@ -15124,7 +15768,7 @@
         <v>19741</v>
       </c>
       <c r="B115" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C115" s="4">
         <v>44</v>
@@ -15160,25 +15804,61 @@
       <c t="s" r="N115" s="4">
         <v>52</v>
       </c>
-      <c r="O115" s="5"/>
-      <c r="P115" s="5"/>
-      <c r="Q115" s="6"/>
-      <c r="R115" s="7"/>
-      <c r="S115" s="6"/>
-      <c r="T115" s="6"/>
-      <c r="U115" s="6"/>
-      <c r="V115" s="6"/>
-      <c r="W115" s="6"/>
-      <c r="X115" s="8"/>
-      <c r="Y115" s="6"/>
-      <c r="Z115" s="6"/>
-      <c r="AA115" s="8"/>
-      <c r="AB115" s="8"/>
-      <c r="AC115" s="8"/>
-      <c r="AD115" s="8"/>
-      <c r="AE115" s="6"/>
+      <c r="O115" s="5">
+        <v>2944.6999999999998</v>
+      </c>
+      <c r="P115" s="5">
+        <v>2944.6999999999998</v>
+      </c>
+      <c r="Q115" s="6">
+        <v>-0.20574511126095751</v>
+      </c>
+      <c r="R115" s="7">
+        <v>34</v>
+      </c>
+      <c r="S115" s="6">
+        <v>-0.26086956521739135</v>
+      </c>
+      <c r="T115" s="6">
+        <v>0.23253526675043298</v>
+      </c>
+      <c r="U115" s="6">
+        <v>-0.052974292797228928</v>
+      </c>
+      <c r="V115" s="6">
+        <v>0.032608584915271507</v>
+      </c>
+      <c r="W115" s="6">
+        <v>-0.0078505450470336535</v>
+      </c>
+      <c r="X115" s="8">
+        <v>28.536310714285715</v>
+      </c>
+      <c r="Y115" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z115" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA115" s="8">
+        <v>7.322857142857143</v>
+      </c>
+      <c r="AB115" s="8">
+        <v>11.591665384615386</v>
+      </c>
+      <c r="AC115" s="8">
+        <v>14.205458999999999</v>
+      </c>
+      <c r="AD115" s="8">
+        <v>20.891667857142856</v>
+      </c>
+      <c r="AE115" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF115" s="9"/>
-      <c r="AG115" s="5"/>
+      <c r="AG115" s="5">
+        <v>0</v>
+      </c>
       <c r="AH115" s="10">
         <v>4</v>
       </c>
@@ -16483,7 +17163,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16519,25 +17199,61 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
-      <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="O126" s="5">
+        <v>2929.0599999999999</v>
+      </c>
+      <c r="P126" s="5">
+        <v>2929.0599999999999</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-0.37945221731650891</v>
+      </c>
+      <c r="R126" s="7">
+        <v>35</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.52702702702702697</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0.00019733293274975589</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.22191829460646076</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.14865724840051076</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.12960676804162427</v>
+      </c>
+      <c r="X126" s="8">
+        <v>43.987355172413793</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>7.3157142857142858</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>15.228571428571428</v>
+      </c>
+      <c r="AC126" s="8">
+        <v>22.258571</v>
+      </c>
+      <c r="AD126" s="8">
+        <v>28.340231034482759</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.20689655172413793</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -17755,7 +18471,7 @@
         <v>19785</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -17791,25 +18507,61 @@
       <c t="s" r="N136" s="4">
         <v>52</v>
       </c>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="6"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="6"/>
-      <c r="T136" s="6"/>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-      <c r="X136" s="8"/>
-      <c r="Y136" s="6"/>
-      <c r="Z136" s="6"/>
-      <c r="AA136" s="8"/>
-      <c r="AB136" s="8"/>
-      <c r="AC136" s="8"/>
-      <c r="AD136" s="8"/>
-      <c r="AE136" s="6"/>
+      <c r="O136" s="5">
+        <v>3496.3099999999999</v>
+      </c>
+      <c r="P136" s="5">
+        <v>3496.3099999999999</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>-0.12188316254771947</v>
+      </c>
+      <c r="R136" s="7">
+        <v>35</v>
+      </c>
+      <c r="S136" s="6">
+        <v>-0.125</v>
+      </c>
+      <c r="T136" s="6">
+        <v>0.25978131229782253</v>
+      </c>
+      <c r="U136" s="6">
+        <v>-0.026503370696534346</v>
+      </c>
+      <c r="V136" s="6">
+        <v>0.012634749207021116</v>
+      </c>
+      <c r="W136" s="6">
+        <v>-0.016624670009238313</v>
+      </c>
+      <c r="X136" s="8">
+        <v>33.587655555555557</v>
+      </c>
+      <c r="Y136" s="6">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Z136" s="6">
+        <v>0.29629629629629628</v>
+      </c>
+      <c r="AA136" s="8">
+        <v>10.45965</v>
+      </c>
+      <c r="AB136" s="8">
+        <v>7.5749999999999993</v>
+      </c>
+      <c r="AC136" s="8">
+        <v>19.205555</v>
+      </c>
+      <c r="AD136" s="8">
+        <v>26.290122222222223</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>0.51851851851851849</v>
+      </c>
       <c r="AF136" s="9"/>
-      <c r="AG136" s="5"/>
+      <c r="AG136" s="5">
+        <v>-192.59999999999999</v>
+      </c>
       <c r="AH136" s="10">
         <v>2</v>
       </c>
@@ -19249,7 +20001,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>44</v>
@@ -19285,25 +20037,61 @@
       <c t="s" r="N148" s="4">
         <v>52</v>
       </c>
-      <c r="O148" s="5"/>
-      <c r="P148" s="5"/>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="7"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-      <c r="V148" s="6"/>
-      <c r="W148" s="6"/>
-      <c r="X148" s="8"/>
-      <c r="Y148" s="6"/>
-      <c r="Z148" s="6"/>
-      <c r="AA148" s="8"/>
-      <c r="AB148" s="8"/>
-      <c r="AC148" s="8"/>
-      <c r="AD148" s="8"/>
-      <c r="AE148" s="6"/>
+      <c r="O148" s="5">
+        <v>9686.0799999999999</v>
+      </c>
+      <c r="P148" s="5">
+        <v>9686.0799999999999</v>
+      </c>
+      <c r="Q148" s="6">
+        <v>0.84056079064031453</v>
+      </c>
+      <c r="R148" s="7">
+        <v>135</v>
+      </c>
+      <c r="S148" s="6">
+        <v>1.0769230769230771</v>
+      </c>
+      <c r="T148" s="6">
+        <v>0.0017344477848624006</v>
+      </c>
+      <c r="U148" s="6">
+        <v>-0.42276545310383562</v>
+      </c>
+      <c r="V148" s="6">
+        <v>0.052937359592322174</v>
+      </c>
+      <c r="W148" s="6">
+        <v>0.026949550282467212</v>
+      </c>
+      <c r="X148" s="8">
+        <v>36.262704918032789</v>
+      </c>
+      <c r="Y148" s="6">
+        <v>0.22131147540983606</v>
+      </c>
+      <c r="Z148" s="6">
+        <v>0.32786885245901637</v>
+      </c>
+      <c r="AA148" s="8">
+        <v>12.711851851851851</v>
+      </c>
+      <c r="AB148" s="8">
+        <v>14.733823529411763</v>
+      </c>
+      <c r="AC148" s="8">
+        <v>27.606857999999999</v>
+      </c>
+      <c r="AD148" s="8">
+        <v>32.542486065573769</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>0.47540983606557374</v>
+      </c>
       <c r="AF148" s="9"/>
-      <c r="AG148" s="5"/>
+      <c r="AG148" s="5">
+        <v>0</v>
+      </c>
       <c r="AH148" s="10">
         <v>2</v>
       </c>
@@ -19473,7 +20261,7 @@
         <v>19820</v>
       </c>
       <c r="B150" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C150" s="4">
         <v>44</v>
@@ -19509,25 +20297,61 @@
       <c t="s" r="N150" s="4">
         <v>52</v>
       </c>
-      <c r="O150" s="5"/>
-      <c r="P150" s="5"/>
-      <c r="Q150" s="6"/>
-      <c r="R150" s="7"/>
-      <c r="S150" s="6"/>
-      <c r="T150" s="6"/>
-      <c r="U150" s="6"/>
-      <c r="V150" s="6"/>
-      <c r="W150" s="6"/>
-      <c r="X150" s="8"/>
-      <c r="Y150" s="6"/>
-      <c r="Z150" s="6"/>
-      <c r="AA150" s="8"/>
-      <c r="AB150" s="8"/>
-      <c r="AC150" s="8"/>
-      <c r="AD150" s="8"/>
-      <c r="AE150" s="6"/>
+      <c r="O150" s="5">
+        <v>2025.05</v>
+      </c>
+      <c r="P150" s="5">
+        <v>2025.05</v>
+      </c>
+      <c r="Q150" s="6">
+        <v>-0.26488792086396229</v>
+      </c>
+      <c r="R150" s="7">
+        <v>23</v>
+      </c>
+      <c r="S150" s="6">
+        <v>-0.23333333333333328</v>
+      </c>
+      <c r="T150" s="6">
+        <v>0.36063830522703144</v>
+      </c>
+      <c r="U150" s="6">
+        <v>0.0081926866003308556</v>
+      </c>
+      <c r="V150" s="6">
+        <v>0.047601046887731167</v>
+      </c>
+      <c r="W150" s="6">
+        <v>-0.0077901780202957946</v>
+      </c>
+      <c r="X150" s="8">
+        <v>26.9175</v>
+      </c>
+      <c r="Y150" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z150" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="8">
+        <v>2.7898565217391309</v>
+      </c>
+      <c r="AB150" s="8">
+        <v>4.8263157894736848</v>
+      </c>
+      <c r="AC150" s="8">
+        <v>7.5963149999999997</v>
+      </c>
+      <c r="AD150" s="8">
+        <v>14.1625</v>
+      </c>
+      <c r="AE150" s="6">
+        <v>0.75</v>
+      </c>
       <c r="AF150" s="9"/>
-      <c r="AG150" s="5"/>
+      <c r="AG150" s="5">
+        <v>0</v>
+      </c>
       <c r="AH150" s="10">
         <v>3</v>
       </c>
@@ -21385,7 +22209,7 @@
         <v>19879</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -21421,25 +22245,61 @@
       <c t="s" r="N166" s="4">
         <v>52</v>
       </c>
-      <c r="O166" s="5"/>
-      <c r="P166" s="5"/>
-      <c r="Q166" s="6"/>
-      <c r="R166" s="7"/>
-      <c r="S166" s="6"/>
-      <c r="T166" s="6"/>
-      <c r="U166" s="6"/>
-      <c r="V166" s="6"/>
-      <c r="W166" s="6"/>
-      <c r="X166" s="8"/>
-      <c r="Y166" s="6"/>
-      <c r="Z166" s="6"/>
-      <c r="AA166" s="8"/>
-      <c r="AB166" s="8"/>
-      <c r="AC166" s="8"/>
-      <c r="AD166" s="8"/>
-      <c r="AE166" s="6"/>
+      <c r="O166" s="5">
+        <v>2847.8000000000002</v>
+      </c>
+      <c r="P166" s="5">
+        <v>2847.8000000000002</v>
+      </c>
+      <c r="Q166" s="6">
+        <v>0.080021237864077666</v>
+      </c>
+      <c r="R166" s="7">
+        <v>26</v>
+      </c>
+      <c r="S166" s="6">
+        <v>-0.03703703703703709</v>
+      </c>
+      <c r="T166" s="6">
+        <v>0.30466616335416807</v>
+      </c>
+      <c r="U166" s="6">
+        <v>0.036862946836154223</v>
+      </c>
+      <c r="V166" s="6">
+        <v>0.10575900695273543</v>
+      </c>
+      <c r="W166" s="6">
+        <v>0.064341070299880607</v>
+      </c>
+      <c r="X166" s="8">
+        <v>25.026315789473685</v>
+      </c>
+      <c r="Y166" s="6">
+        <v>0.31578947368421051</v>
+      </c>
+      <c r="Z166" s="6">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AA166" s="8">
+        <v>3.1623444444444448</v>
+      </c>
+      <c r="AB166" s="8">
+        <v>7.5061421052631587</v>
+      </c>
+      <c r="AC166" s="8">
+        <v>10.685086999999999</v>
+      </c>
+      <c r="AD166" s="8">
+        <v>17.605263157894736</v>
+      </c>
+      <c r="AE166" s="6">
+        <v>0.94736842105263153</v>
+      </c>
       <c r="AF166" s="9"/>
-      <c r="AG166" s="5"/>
+      <c r="AG166" s="5">
+        <v>-88.799999999999997</v>
+      </c>
       <c r="AH166" s="10">
         <v>3</v>
       </c>
@@ -22528,7 +23388,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22564,25 +23424,61 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
-      <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="O175" s="5">
+        <v>2441.6900000000001</v>
+      </c>
+      <c r="P175" s="5">
+        <v>2441.6900000000001</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>0.0052781746244139338</v>
+      </c>
+      <c r="R175" s="7">
+        <v>32</v>
+      </c>
+      <c r="S175" s="6">
+        <v>-0.085714285714285743</v>
+      </c>
+      <c r="T175" s="6">
+        <v>-0.027357895555946903</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.3635594608652204</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.033422547497839614</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.019163980685508807</v>
+      </c>
+      <c r="X175" s="8">
+        <v>32.184446666666666</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>8.3442517241379317</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>5.2644466666666672</v>
+      </c>
+      <c r="AC175" s="8">
+        <v>13.997776999999999</v>
+      </c>
+      <c r="AD175" s="8">
+        <v>20.94111333333333</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-306</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -23137,7 +24033,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -23173,25 +24069,61 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
-      <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="O180" s="5">
+        <v>2521.52</v>
+      </c>
+      <c r="P180" s="5">
+        <v>2521.52</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>-0.46106857829244619</v>
+      </c>
+      <c r="R180" s="7">
+        <v>33</v>
+      </c>
+      <c r="S180" s="6">
+        <v>-0.4107142857142857</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.34403455058853388</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.0074133855769535845</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.071273279609124662</v>
+      </c>
+      <c r="X180" s="8">
+        <v>49.444049999999997</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>8.0713531249999999</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>22.671428571428571</v>
+      </c>
+      <c r="AC180" s="8">
+        <v>31.409523</v>
+      </c>
+      <c r="AD180" s="8">
+        <v>39.346428571428575</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.071428571428571425</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>-109.2</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -23232,7 +24164,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23268,25 +24200,61 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
-      <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="O181" s="5">
+        <v>2743.6999999999998</v>
+      </c>
+      <c r="P181" s="5">
+        <v>2743.6999999999998</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.28697406069703058</v>
+      </c>
+      <c r="R181" s="7">
+        <v>30</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="T181" s="6">
+        <v>-0.12219265954732661</v>
+      </c>
+      <c r="U181" s="6">
+        <v>-0.39080803294820865</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.12383842985749173</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.083801253781390098</v>
+      </c>
+      <c r="X181" s="8">
+        <v>17.198414285714286</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>4.0194433333333333</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>2.552775</v>
+      </c>
+      <c r="AC181" s="8">
+        <v>6.7900780000000003</v>
+      </c>
+      <c r="AD181" s="8">
+        <v>12.588095238095239</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23908,7 +24876,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23944,25 +24912,61 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
-      <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="O187" s="5">
+        <v>1697.9000000000001</v>
+      </c>
+      <c r="P187" s="5">
+        <v>1697.9000000000001</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>0.14136864748588351</v>
+      </c>
+      <c r="R187" s="7">
+        <v>24</v>
+      </c>
+      <c r="S187" s="6">
+        <v>0.14285714285714279</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.34016137581718586</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.1211316920902291</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.066917662995464977</v>
+      </c>
+      <c r="X187" s="8">
+        <v>46.455558333333329</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>7.6868041666666675</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>16.620833333333334</v>
+      </c>
+      <c r="AC187" s="8">
+        <v>24.438887999999999</v>
+      </c>
+      <c r="AD187" s="8">
+        <v>31.394441666666665</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.083333333333333329</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-165.40000000000001</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -24136,7 +25140,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24172,25 +25176,61 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
-      <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="O189" s="5">
+        <v>4451.6300000000001</v>
+      </c>
+      <c r="P189" s="5">
+        <v>4451.6300000000001</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.5046000243351767</v>
+      </c>
+      <c r="R189" s="7">
+        <v>67</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.39583333333333326</v>
+      </c>
+      <c r="T189" s="6">
+        <v>2.0940523358859564</v>
+      </c>
+      <c r="U189" s="6">
+        <v>1.7562008073447253</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.047120155987806715</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.013485285165209148</v>
+      </c>
+      <c r="X189" s="8">
+        <v>28.530468750000001</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.140625</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.046875</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>5.674754411764706</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>10.358995238095238</v>
+      </c>
+      <c r="AC189" s="8">
+        <v>16.053525</v>
+      </c>
+      <c r="AD189" s="8">
+        <v>22.805468749999999</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.71875</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24231,7 +25271,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24267,25 +25307,61 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
-      <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="O190" s="5">
+        <v>3769.0700000000002</v>
+      </c>
+      <c r="P190" s="5">
+        <v>3769.0700000000002</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.11670357741296677</v>
+      </c>
+      <c r="R190" s="7">
+        <v>42</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T190" s="6">
+        <v>-2.3265051060341144</v>
+      </c>
+      <c r="U190" s="6">
+        <v>-2.9396988116431904</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.056023501818751043</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.026570612909815949</v>
+      </c>
+      <c r="X190" s="8">
+        <v>26.754384210526315</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>3.8424595238095236</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>8.4263157894736835</v>
+      </c>
+      <c r="AC190" s="8">
+        <v>12.741315</v>
+      </c>
+      <c r="AD190" s="8">
+        <v>19.588594736842104</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-87.900000000000006</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24926,7 +26002,9 @@
       <c r="AB195" s="8">
         <v>10.942735897435897</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>16.401281999999998</v>
+      </c>
       <c r="AD195" s="8">
         <v>23.329058974358976</v>
       </c>
@@ -25370,7 +26448,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25406,25 +26484,61 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
-      <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="O199" s="5">
+        <v>3253.1300000000001</v>
+      </c>
+      <c r="P199" s="5">
+        <v>3253.1300000000001</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.0106774444687735</v>
+      </c>
+      <c r="R199" s="7">
+        <v>35</v>
+      </c>
+      <c r="S199" s="6">
+        <v>0.029411764705882248</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.36436702498824208</v>
+      </c>
+      <c r="U199" s="6">
+        <v>-0.01679511731778318</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.013965165855652864</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-0.019442659838371044</v>
+      </c>
+      <c r="X199" s="8">
+        <v>38.896664999999999</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>5.0606472222222223</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>13.330834999999999</v>
+      </c>
+      <c r="AC199" s="8">
+        <v>19.039563000000001</v>
+      </c>
+      <c r="AD199" s="8">
+        <v>25.854165000000002</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-20.93</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -25465,7 +26579,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25501,25 +26615,61 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
-      <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="O200" s="5">
+        <v>1337.98</v>
+      </c>
+      <c r="P200" s="5">
+        <v>1337.98</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.5029261443414772</v>
+      </c>
+      <c r="R200" s="7">
+        <v>18</v>
+      </c>
+      <c r="S200" s="6">
+        <v>0.38461538461538458</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.32019163216191576</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.16421209584597676</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.086460559948579208</v>
+      </c>
+      <c r="X200" s="8">
+        <v>24.073608333333336</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>7.3777777777777782</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>2.3180583333333336</v>
+      </c>
+      <c r="AC200" s="8">
+        <v>10.426387999999999</v>
+      </c>
+      <c r="AD200" s="8">
+        <v>17.379166666666666</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.91666666666666663</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-226.09</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -26008,7 +27158,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>44</v>
@@ -26044,25 +27194,57 @@
       <c t="s" r="N205" s="4">
         <v>52</v>
       </c>
-      <c r="O205" s="5"/>
-      <c r="P205" s="5"/>
+      <c r="O205" s="5">
+        <v>3019.6799999999998</v>
+      </c>
+      <c r="P205" s="5">
+        <v>3019.6799999999998</v>
+      </c>
       <c r="Q205" s="6"/>
-      <c r="R205" s="7"/>
+      <c r="R205" s="7">
+        <v>37</v>
+      </c>
       <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="8"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="8"/>
-      <c r="AB205" s="8"/>
-      <c r="AC205" s="8"/>
-      <c r="AD205" s="8"/>
-      <c r="AE205" s="6"/>
+      <c r="T205" s="6">
+        <v>0.00034208922799766861</v>
+      </c>
+      <c r="U205" s="6">
+        <v>-0.34402221427436019</v>
+      </c>
+      <c r="V205" s="6">
+        <v>0.036045872410321624</v>
+      </c>
+      <c r="W205" s="6">
+        <v>0.004022611667461453</v>
+      </c>
+      <c r="X205" s="8">
+        <v>22.533330769230766</v>
+      </c>
+      <c r="Y205" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="8">
+        <v>5.4226861111111111</v>
+      </c>
+      <c r="AB205" s="8">
+        <v>1.5954545454545455</v>
+      </c>
+      <c r="AC205" s="8">
+        <v>7.0236590000000003</v>
+      </c>
+      <c r="AD205" s="8">
+        <v>13.39743846153846</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>0.92307692307692313</v>
+      </c>
       <c r="AF205" s="9"/>
-      <c r="AG205" s="5"/>
+      <c r="AG205" s="5">
+        <v>-249.09999999999999</v>
+      </c>
       <c r="AH205" s="10">
         <v>3</v>
       </c>
@@ -27161,7 +28343,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>
@@ -27197,25 +28379,57 @@
       <c t="s" r="N216" s="4">
         <v>52</v>
       </c>
-      <c r="O216" s="5"/>
-      <c r="P216" s="5"/>
+      <c r="O216" s="5">
+        <v>6616.6999999999998</v>
+      </c>
+      <c r="P216" s="5">
+        <v>6616.6999999999998</v>
+      </c>
       <c r="Q216" s="6"/>
-      <c r="R216" s="7"/>
+      <c r="R216" s="7">
+        <v>80</v>
+      </c>
       <c r="S216" s="6"/>
-      <c r="T216" s="6"/>
-      <c r="U216" s="6"/>
-      <c r="V216" s="6"/>
-      <c r="W216" s="6"/>
-      <c r="X216" s="8"/>
-      <c r="Y216" s="6"/>
-      <c r="Z216" s="6"/>
-      <c r="AA216" s="8"/>
-      <c r="AB216" s="8"/>
-      <c r="AC216" s="8"/>
-      <c r="AD216" s="8"/>
-      <c r="AE216" s="6"/>
+      <c r="T216" s="6">
+        <v>8.735472365378512E-05</v>
+      </c>
+      <c r="U216" s="6">
+        <v>-0.34028473408194415</v>
+      </c>
+      <c r="V216" s="6">
+        <v>0.04261122613991869</v>
+      </c>
+      <c r="W216" s="6">
+        <v>0.0084552269258089379</v>
+      </c>
+      <c r="X216" s="8">
+        <v>37.291818181818186</v>
+      </c>
+      <c r="Y216" s="6">
+        <v>0.89090909090909087</v>
+      </c>
+      <c r="Z216" s="6">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="AA216" s="8">
+        <v>10.27818888888889</v>
+      </c>
+      <c r="AB216" s="8">
+        <v>12.456060000000001</v>
+      </c>
+      <c r="AC216" s="8">
+        <v>22.835298999999999</v>
+      </c>
+      <c r="AD216" s="8">
+        <v>30.151514545454546</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>0.30909090909090908</v>
+      </c>
       <c r="AF216" s="9"/>
-      <c r="AG216" s="5"/>
+      <c r="AG216" s="5">
+        <v>-195.90000000000001</v>
+      </c>
       <c r="AH216" s="10"/>
       <c r="AI216" s="11"/>
       <c r="AJ216" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-15).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-15).xlsx
@@ -915,51 +915,48 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 907.654,06</t>
-  </si>
-  <si>
-    <t>R$ 4.932,90
-R$ 5.074,50</t>
-  </si>
-  <si>
-    <t>11.4%
-14.6%</t>
+173</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 918.125,02</t>
+  </si>
+  <si>
+    <t>R$ 4.936,16
+R$ 5.076,36</t>
+  </si>
+  <si>
+    <t>12.1%
+15.2%</t>
   </si>
   <si>
     <t>55.0</t>
   </si>
   <si>
-    <t>8.1%</t>
-  </si>
-  <si>
-    <t>42.1%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>41.8%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>3.5%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
     <t>27.2</t>
   </si>
   <si>
-    <t>67.8%</t>
+    <t>67.9%</t>
   </si>
   <si>
     <t>10.5%</t>
   </si>
   <si>
-    <t>5.2</t>
+    <t>5.3</t>
   </si>
   <si>
     <t>7.4</t>
@@ -974,7 +971,7 @@
     <t>72.2%</t>
   </si>
   <si>
-    <t>-R$ 20.504,06</t>
+    <t>-R$ 20.591,86</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3928,7 +3925,7 @@
         <v>0.012969093465047821</v>
       </c>
       <c r="W20" s="6">
-        <v>-0.0078710266275749327</v>
+        <v>-0.0075491752681197902</v>
       </c>
       <c r="X20" s="8">
         <v>24.648684210526316</v>
@@ -4840,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -6713,7 +6710,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6749,25 +6746,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>5840.1599999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>5840.1599999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.70365400435236669</v>
+      </c>
+      <c r="R42" s="7">
+        <v>46</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.251812381852552</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.049660522999369877</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.054792077614311943</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.020885472315826964</v>
+      </c>
+      <c r="X42" s="8">
+        <v>27.378470833333335</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.0287500000000005</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>4.1937500000000005</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>11.310416</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.256249999999998</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -8152,7 +8185,9 @@
       <c r="AB53" s="8">
         <v>2.901332</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>6.3966659999999997</v>
+      </c>
       <c r="AD53" s="8">
         <v>13.347999999999999</v>
       </c>
@@ -12080,7 +12115,7 @@
         <v>19687</v>
       </c>
       <c r="B85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C85" s="4">
         <v>44</v>
@@ -12116,25 +12151,61 @@
       <c t="s" r="N85" s="4">
         <v>52</v>
       </c>
-      <c r="O85" s="5"/>
-      <c r="P85" s="5"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="7"/>
-      <c r="S85" s="6"/>
-      <c r="T85" s="6"/>
-      <c r="U85" s="6"/>
-      <c r="V85" s="6"/>
-      <c r="W85" s="6"/>
-      <c r="X85" s="8"/>
-      <c r="Y85" s="6"/>
-      <c r="Z85" s="6"/>
-      <c r="AA85" s="8"/>
-      <c r="AB85" s="8"/>
-      <c r="AC85" s="8"/>
-      <c r="AD85" s="8"/>
-      <c r="AE85" s="6"/>
+      <c r="O85" s="5">
+        <v>4630.8000000000002</v>
+      </c>
+      <c r="P85" s="5">
+        <v>4630.8000000000002</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>2.0832329069930022</v>
+      </c>
+      <c r="R85" s="7">
+        <v>57</v>
+      </c>
+      <c r="S85" s="6">
+        <v>1.7142857142857144</v>
+      </c>
+      <c r="T85" s="6">
+        <v>0</v>
+      </c>
+      <c r="U85" s="6">
+        <v>-0.32388356223546683</v>
+      </c>
+      <c r="V85" s="6">
+        <v>0.016237043275459963</v>
+      </c>
+      <c r="W85" s="6">
+        <v>0.0094606763410209887</v>
+      </c>
+      <c r="X85" s="8">
+        <v>32.125</v>
+      </c>
+      <c r="Y85" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA85" s="8">
+        <v>8.0905235294117634</v>
+      </c>
+      <c r="AB85" s="8">
+        <v>8.7861166666666666</v>
+      </c>
+      <c r="AC85" s="8">
+        <v>14.278535</v>
+      </c>
+      <c r="AD85" s="8">
+        <v>17.4020875</v>
+      </c>
+      <c r="AE85" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF85" s="9"/>
-      <c r="AG85" s="5"/>
+      <c r="AG85" s="5">
+        <v>-87.799999999999997</v>
+      </c>
       <c r="AH85" s="10">
         <v>3</v>
       </c>
@@ -14148,7 +14219,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -14265,7 +14336,9 @@
       <c r="AB102" s="8">
         <v>23.126315789473683</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>30.66441</v>
+      </c>
       <c r="AD102" s="8">
         <v>33.951585714285713</v>
       </c>
@@ -15947,7 +16020,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>10.767296999999999</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -20062,7 +20137,7 @@
         <v>0.052937359592322174</v>
       </c>
       <c r="W148" s="6">
-        <v>0.026949550282467212</v>
+        <v>0.036237105206647066</v>
       </c>
       <c r="X148" s="8">
         <v>36.262704918032789</v>
@@ -24652,7 +24727,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25623,7 +25698,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -26934,7 +27009,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28507,41 +28582,41 @@
         <v>310</v>
       </c>
       <c t="s" r="W217" s="14">
+        <v>309</v>
+      </c>
+      <c t="s" r="X217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="X217" s="14">
+      <c t="s" r="Y217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Y217" s="14">
+      <c t="s" r="Z217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="Z217" s="14">
+      <c t="s" r="AA217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AA217" s="14">
+      <c t="s" r="AB217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AB217" s="14">
+      <c t="s" r="AC217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AC217" s="14">
+      <c t="s" r="AD217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AD217" s="14">
+      <c t="s" r="AE217" s="14">
         <v>318</v>
-      </c>
-      <c t="s" r="AE217" s="14">
-        <v>319</v>
       </c>
       <c r="AF217" s="14"/>
       <c t="s" r="AG217" s="14">
+        <v>319</v>
+      </c>
+      <c t="s" r="AH217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AH217" s="14">
+      <c t="s" r="AI217" s="14">
         <v>321</v>
-      </c>
-      <c t="s" r="AI217" s="14">
-        <v>322</v>
       </c>
       <c r="AJ217" s="15"/>
       <c t="s" r="AK217" s="15">
@@ -28551,10 +28626,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM217" s="14">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN217" s="14">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AO217" s="15"/>
       <c r="AP217" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-15).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-15).xlsx
@@ -915,63 +915,66 @@
   </si>
   <si>
     <t>215
-173</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 918.125,02</t>
-  </si>
-  <si>
-    <t>R$ 4.936,16
-R$ 5.076,36</t>
-  </si>
-  <si>
-    <t>12.1%
-15.2%</t>
-  </si>
-  <si>
-    <t>55.0</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>41.8%</t>
+178</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 939.956,32</t>
+  </si>
+  <si>
+    <t>R$ 4.921,24
+R$ 5.056,41</t>
+  </si>
+  <si>
+    <t>12.5%
+15.4%</t>
+  </si>
+  <si>
+    <t>54.8</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>27.2</t>
-  </si>
-  <si>
-    <t>67.9%</t>
-  </si>
-  <si>
-    <t>10.5%</t>
+    <t>27.1</t>
+  </si>
+  <si>
+    <t>68.2%</t>
+  </si>
+  <si>
+    <t>10.2%</t>
   </si>
   <si>
     <t>5.3</t>
   </si>
   <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>12.8</t>
-  </si>
-  <si>
-    <t>19.2</t>
-  </si>
-  <si>
-    <t>72.2%</t>
-  </si>
-  <si>
-    <t>-R$ 20.591,86</t>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>12.7</t>
+  </si>
+  <si>
+    <t>19.1</t>
+  </si>
+  <si>
+    <t>72.8%</t>
+  </si>
+  <si>
+    <t>-R$ 20.555,86</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1411,7 +1414,7 @@
     <col min="14" max="14" width="12.14" customWidth="1"/>
     <col min="15" max="15" width="15.29" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="6.86" customWidth="1"/>
+    <col min="17" max="17" width="7.71" customWidth="1"/>
     <col min="18" max="18" width="10.14" customWidth="1"/>
     <col min="19" max="19" width="13.71" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
@@ -2066,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>12108.67</v>
+      </c>
+      <c r="P6" s="5">
+        <v>12108.67</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.62256103362192472</v>
+      </c>
+      <c r="R6" s="7">
+        <v>126</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.53658536585365857</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.27436448429100802</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0091084322225314582</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.026294043854527376</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.00053729270018920325</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.071306185567014</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.79381443298969068</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.7252100840336126</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.25</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>9.1792090000000002</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>16.129553608247424</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.95876288659793818</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7883,7 +7922,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7919,25 +7958,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>687.13</v>
+      </c>
+      <c r="P51" s="5">
+        <v>687.13</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.3792252107587315</v>
+      </c>
+      <c r="R51" s="7">
+        <v>7</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.30119482485119264</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.13703738739394292</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.049259237698834279</v>
+      </c>
+      <c r="X51" s="8">
+        <v>34.461100000000002</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.2166714285714284</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>16.877766666666666</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>26.62223333333333</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8810,7 +8883,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>14.152139999999999</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20469,7 +20544,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20505,25 +20580,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>3158.3899999999999</v>
+      </c>
+      <c r="P151" s="5">
+        <v>3158.3899999999999</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>0.26826163600807917</v>
+      </c>
+      <c r="R151" s="7">
+        <v>34</v>
+      </c>
+      <c r="S151" s="6">
+        <v>0.17241379310344818</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.298361791925633</v>
+      </c>
+      <c r="U151" s="6">
+        <v>0.0066942017926855148</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.043534997261262857</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.0012792910311899416</v>
+      </c>
+      <c r="X151" s="8">
+        <v>22.462644827586207</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>3.9076199999999996</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.6691370370370371</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>6.536238</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>13.068965517241379</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.93103448275862066</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21219,7 +21330,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21255,25 +21366,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>3552.0100000000002</v>
+      </c>
+      <c r="P157" s="5">
+        <v>3552.0100000000002</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>0.40998098595183374</v>
+      </c>
+      <c r="R157" s="7">
+        <v>41</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.28102342054217189</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.0063209281505401168</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.030332262578089585</v>
+      </c>
+      <c r="W157" s="6">
+        <v>-6.1795997195953836E-05</v>
+      </c>
+      <c r="X157" s="8">
+        <v>21.417187500000001</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>5.5991461538461538</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.2890625</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>9.1963530000000002</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>16.143228125</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.96875</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21314,7 +21461,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21350,11 +21497,21 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
+      <c r="O158" s="5">
+        <v>0</v>
+      </c>
+      <c r="P158" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R158" s="7">
+        <v>0</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-1</v>
+      </c>
       <c r="T158" s="6"/>
       <c r="U158" s="6"/>
       <c r="V158" s="6"/>
@@ -21368,7 +21525,9 @@
       <c r="AD158" s="8"/>
       <c r="AE158" s="6"/>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22189,7 +22348,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22225,25 +22384,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>2325.0999999999999</v>
+      </c>
+      <c r="P165" s="5">
+        <v>2325.0999999999999</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>-0.51284667587154797</v>
+      </c>
+      <c r="R165" s="7">
+        <v>27</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.28704911616704659</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0013728871876478432</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.038458345877596667</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.020924046277579461</v>
+      </c>
+      <c r="X165" s="8">
+        <v>17.094926086956519</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>4.0524703703703704</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>1.008695652173913</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>5.2260859999999996</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>12.122465217391305</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>36</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
@@ -28582,41 +28777,41 @@
         <v>310</v>
       </c>
       <c t="s" r="W217" s="14">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="X217" s="14">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="Y217" s="14">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="Z217" s="14">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="AA217" s="14">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="AB217" s="14">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="AC217" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AD217" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="AE217" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AF217" s="14"/>
       <c t="s" r="AG217" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AH217" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="AI217" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AJ217" s="15"/>
       <c t="s" r="AK217" s="15">
@@ -28626,10 +28821,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM217" s="14">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="AN217" s="14">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO217" s="15"/>
       <c r="AP217" s="15"/>
